--- a/Acess Matrix.xlsx
+++ b/Acess Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B655E6D8-92CC-4229-B76F-AA256D278689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E972937D-13ED-4DB9-85DF-0B96E7433919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6696B59A-C62D-4AA5-A1DB-F37A4A4F47B5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t>Team</t>
   </si>
@@ -56,22 +56,10 @@
     <t>Cloud Admins</t>
   </si>
   <si>
-    <t>Owner</t>
-  </si>
-  <si>
     <t>Developers</t>
   </si>
   <si>
     <t>Contributor</t>
-  </si>
-  <si>
-    <t>No Access</t>
-  </si>
-  <si>
-    <t>Reader</t>
-  </si>
-  <si>
-    <t>Support</t>
   </si>
 </sst>
 </file>
@@ -95,20 +83,41 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -117,11 +126,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -457,63 +466,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E78142-46E0-4881-A610-7D278AB562F8}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="16.6640625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
